--- a/templates/mfi-cdf-input.xlsx
+++ b/templates/mfi-cdf-input.xlsx
@@ -1052,13 +1052,13 @@
       <c r="U1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="6" t="s">
         <v>86</v>
       </c>
       <c r="Y1" s="6" t="s">
